--- a/week3/auto_output/auto_excel/001282_三联锻造_auto.xlsx
+++ b/week3/auto_output/auto_excel/001282_三联锻造_auto.xlsx
@@ -1,14 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="1_认缴流量" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="2_股权结构存量" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1_认缴流量" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2_股权结构存量" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3_交叉校验" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4_股权转让" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1819,4 +1821,424 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>校验类型</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>批次/时点</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>认购方数量</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>合计金额(万元)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>合计股数(万股)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>批次汇总</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>第1批</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" s="2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>批次汇总</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>第2批</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="2" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>批次汇总</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>第3批</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="2" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>批次汇总</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>第4批</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>1150</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="2" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>批次汇总</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>第5批</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="2" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>批次汇总</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>第6批</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>1566</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>348</v>
+      </c>
+      <c r="F7" s="2" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>股东持股加总</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>2004-06-18设立后</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>股东持股加总</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>2007-12增资后</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>股东持股加总</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>2014-05增资后</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>股东持股加总</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>2017-02增资后</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>股东持股加总</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>2017-11增资后</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>股东持股加总</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>t0/报告期初</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>8498</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>8498</v>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="80" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>PDF页码</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>转让日期</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>转让方</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>受让方</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>转让数量(万股)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>转让价格(元/股)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>转让金额(万元)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>原文证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>自动化提取暂不支持股权转让Sheet，此Sheet需人工补全。Gold标准中已包含。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>